--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>MTN</t>
   </si>
@@ -656,416 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>258600</v>
+      </c>
+      <c r="F8" s="3">
         <v>269800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1238400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1101700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>279400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>267100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1176700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>906500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>175600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>204200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>889100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>684600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>131800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>77200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>694100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>924600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>267800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>244000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>958000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>849600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>220000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>211600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>844500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>734600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>220900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>209100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>794600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>725200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>178300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>541100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>292100</v>
+      </c>
+      <c r="F9" s="3">
         <v>272600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>527900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>588700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>276200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>240500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>475200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>417000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>209400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>218200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>355800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>333000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>172700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>129900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>329600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>456500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>271700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>240800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>410600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>415500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>230400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>214200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>355500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>355900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>218600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>23400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>408100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>420800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>233800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>536900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="F10" s="3">
         <v>-2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>710500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>513000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>26600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>701500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>489500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-33800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-14000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>533300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>351600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-40900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>364500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>468100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-3900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>547400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>434100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-10400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>489000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>378700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>185700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>386500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>304400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1124,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1218,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,58 +1316,64 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>100</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2600</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>13200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>28400</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1347,11 +1387,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1362,112 +1402,124 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>66700</v>
+      </c>
+      <c r="F15" s="3">
         <v>68800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>69100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>66000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>64600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>63200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>65700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>62100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>61500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>63200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>64100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>62700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>62600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>63200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>64700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>63800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>57800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>56600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>55300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>55200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>51000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>50300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>54100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>51400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>48600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>48900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>50000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>49600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>40600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1549,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>727400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>465600</v>
+      </c>
+      <c r="F17" s="3">
         <v>429900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>737900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>773700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>442800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>365300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>636300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>581400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>341200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>374600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>501400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>476900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>295700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>247300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>475900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>613900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>403300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>364600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>535400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>547700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>347600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>324600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>476500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>477000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>324600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>311700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>474600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>472900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>268800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>350600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-160100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>500500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>328000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-163400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-98200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>540400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>325100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-165600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-170400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>387700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>207700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-163900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>218200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>310700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-135500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-120600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>422600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>301900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-127600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-113000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>368000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>257600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>320000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>252300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1781,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F20" s="3">
         <v>8800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>9500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>6500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-7500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>10700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>15900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>5300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-140700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-82500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>575700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>403500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-101700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-31900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>605600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>385400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-101300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-108500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>457300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>276900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-96500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-101200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>275500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>374300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-75900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-60900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>476700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>358200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-77500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-64300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>413900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>319600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>370800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>303200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>40700</v>
+      </c>
+      <c r="F22" s="3">
         <v>40200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>39100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>38400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>35300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>36100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>35100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>37400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>39500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>39100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>39000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>37800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>35400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>33400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>24500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>26100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>22700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>20300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>19600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>21000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>18600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>16400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>15600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>16000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>15200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>9800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>23300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>9000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>12000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>317300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-248200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-191500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>467500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>299200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-201600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-131200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>504800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>286000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-202400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-210900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>354200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>176400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-194500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-197800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>186300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>284300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-156400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-137700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>401900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>282000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-147100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-131000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>344200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>252300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>297500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>244500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-65200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-56900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>124300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>79000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-58000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-21600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>118200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>52000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-59900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-65900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>76900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>27200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-37500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>26400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>67300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-46600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-45400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>93300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>64000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-36400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-46800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>71900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>68200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>100600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>84800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2365,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>229800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-183000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-134600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>343200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>220100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-143600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-109700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>386600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>233900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-142500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-144900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>277300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>149100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-157000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-158000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>159800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>217000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-109800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-92300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>308500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>218000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-110700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-84200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>272300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>184100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>196900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>159700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-175500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-128600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>325000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>208700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-137000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-108700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>372600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>223400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-139300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-140800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>274600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>147800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-153800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-153600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>152500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>206400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-106500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-89500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>292100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>206300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-107800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-80100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>256300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>171100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>181100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>149200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2659,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2590,11 +2712,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2608,20 +2730,20 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2757,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2953,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-9500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-6500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>7500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>8200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>6500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-175500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-128600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>325000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>208700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-137000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-108700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>372600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>223400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-139300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-140800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>274600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>147800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-153800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-153600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>152500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>206400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-106500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-89500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>292100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>206300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-107800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-83700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>256300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>235700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>181100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>149200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3247,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-175500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-128600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>325000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>208700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-137000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-108700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>372600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>223400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-139300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-140800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>274600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>147800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-153800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-153600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>152500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>206400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-106500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-89500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>292100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>206300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-107800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-83700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>256300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>235700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>181100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>149200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3524,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>812200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>728900</v>
+      </c>
+      <c r="F41" s="3">
         <v>563000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>896100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1295300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1180900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1107400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1401200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1407000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1468400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1244000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1344700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1301000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>462200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>391000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>482700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>126800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>136300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>108900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>59600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>158600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>141000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>178100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>181600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>235500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>140400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>117400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>195800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>140900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>106800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,376 +3716,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>105500</v>
+      </c>
+      <c r="F43" s="3">
         <v>381100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>351600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>160400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>118500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>383400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>267100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>167100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>109000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>345400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>208100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>117000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>208500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>106700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>100200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>105300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>87300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>270900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>273100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>87700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>74200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>230800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>220200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>85400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>84600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>186900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>174400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>80800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>59400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>157700</v>
+      </c>
+      <c r="F44" s="3">
         <v>132500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>103600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>122100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>139900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>108700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>92600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>104600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>103700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>80300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>73000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>86900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>100900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>101900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>101700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>113900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>127900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>96500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>84100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>103000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>115000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>85600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>79400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>97500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>108100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>84800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>77300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>93400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>112800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>142400</v>
+      </c>
+      <c r="F45" s="3">
         <v>131500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>131100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>182400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>182300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>192000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>84500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>88700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>96800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>75900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>58900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>68600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>70000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>65600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>66200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>67800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>76800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>51700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>50100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>66000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>62800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>44200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>38500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>62600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>62700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>44000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>51100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>58700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>53400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1178800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1134500</v>
+      </c>
+      <c r="F46" s="3">
         <v>1208100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1482400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1760100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1621700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1791500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1845400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1767400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1777900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1745600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1684800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1573500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>841600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>665100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>750900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>413800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>428300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>527900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>466900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>415300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>393000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>538700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>519700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>481000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>395700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>433100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>498700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>373700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>332400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3967,14 +4177,14 @@
         <v>0</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>101700</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
@@ -3996,192 +4206,210 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2626000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2618200</v>
+      </c>
+      <c r="F48" s="3">
         <v>2654100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2660300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2712400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2600900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2406100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2435700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2484300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2365600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2368200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2424600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2471000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2482200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2515300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2515700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2588100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2606700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1943500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1948700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1932800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1826000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1627200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1640700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2004000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1968500</v>
+      </c>
+      <c r="F49" s="3">
         <v>2029700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2000600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2033700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1996100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2069000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2067600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2082200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2109800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2100200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2124800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2079900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2025300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2023800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1983300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2071400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2081600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1914400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1903400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1853000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1851200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1756300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1772500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4598,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="F52" s="3">
         <v>55900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>56100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>58700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>62200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>51400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>48600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>35800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>37300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>37100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>42500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>41500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>41400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>40100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>39800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>40400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>41000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>40200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>42800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>43900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>44000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>142800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>142600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>146500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>146800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>148800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>152600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>155000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>151400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4794,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5847700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5760000</v>
+      </c>
+      <c r="F54" s="3">
         <v>5947800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6199500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6565000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6280900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6318000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6397300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6369700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6290600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6251100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6276600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6165800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5390500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5244200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>5289700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5113700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5157700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4426100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4361700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>4244900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>4215900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4065000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4075400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,156 +4968,164 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>161600</v>
+      </c>
+      <c r="F57" s="3">
         <v>148500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>114200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>179200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>162400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>151300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>104100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>137900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>116500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>98300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>64400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>86300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>74600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>59700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>62100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>126800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>141700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>96400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>80200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>106200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>118600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>80800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>58200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>94700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>103500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>71600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>51300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>88800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>90800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="F58" s="3">
         <v>69200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>69000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>69600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>67800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>63700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>63700</v>
       </c>
       <c r="J58" s="3">
         <v>63700</v>
       </c>
       <c r="K58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="L58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="M58" s="3">
         <v>114800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>114100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>113500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>112800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>63700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>63700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>63600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>63600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>63800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>48500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>48500</v>
       </c>
       <c r="V58" s="3">
         <v>48500</v>
@@ -4866,13 +5134,13 @@
         <v>48500</v>
       </c>
       <c r="X58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>38500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>38400</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>38400</v>
       </c>
       <c r="AA58" s="3">
         <v>38400</v>
@@ -4890,378 +5158,408 @@
         <v>38400</v>
       </c>
       <c r="AF58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AH58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1028800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1131600</v>
+      </c>
+      <c r="F59" s="3">
         <v>913000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>803200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1039100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1112500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>895800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>662000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>953400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1036500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>766000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>539200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>783400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>811900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>480100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>429700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>728000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>766000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>574200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>486100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>607100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>623300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>474400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>401100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>526400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>567600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>494600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>400700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>503600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>525900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1228800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1362800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1130700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>986400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1287900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1342700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1110900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>829900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1155000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1267800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>978400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>717100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>982500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>950200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>603500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>555400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>918400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>971500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>719100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>614900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>761800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>790400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>593600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>497800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>659500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>709600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>604600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>490400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>630800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>655000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2721600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2732000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2750700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2773700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2789800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2769700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2670300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2687500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2695600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2704600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2736200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2740000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2768000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2387900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2387100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2365400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1817100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2005100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1527700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1310900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1345300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1487000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1234300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1078000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>746600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>737000</v>
+      </c>
+      <c r="F62" s="3">
         <v>730700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>839800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>709800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>616700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>689400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>814800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>725400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>651700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>707400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>792900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>728900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>676700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>722000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>738600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>728000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>658800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>452400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>542700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>454800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>388700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>425400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>495500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>434200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>427300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>473200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>562000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>454400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>370500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5846,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5017800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5127000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4943800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4925500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5102400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5016000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4705600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4568000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4804200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4858100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4656500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4494400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4705100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4224400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3927500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>3867500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3688200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3855300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2925500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>2695400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>2781600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>2876300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2475600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2304800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6372,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>760800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>619700</v>
+      </c>
+      <c r="F72" s="3">
         <v>873700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1081000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>837600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>705900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>895900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1081500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>786500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>598800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>773800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>914600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>639900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>492100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>645900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>799500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>717600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>582200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>759800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>920300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>699000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>551900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>726700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>869900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>673100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>480000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>551000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>650300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>511500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>394700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6764,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>829900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>633000</v>
+      </c>
+      <c r="F76" s="3">
         <v>1003900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1273900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1462600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1264900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1612400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1829300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1565500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1432500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1594600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1782200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1460700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1166100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1316700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1422100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1425500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1302500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1500600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1666400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1463300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1339600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1589400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1770700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6960,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>219300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-175500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-128600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>325000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>208700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-137000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-108700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>372600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>223400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-139300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-140800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>274600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>147800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-153800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-153600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>152500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>206400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-106500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-89500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>292100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>206300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-107800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-83700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>256300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>235700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>181100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>149200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7201,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>66700</v>
+      </c>
+      <c r="F83" s="3">
         <v>68800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>69100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>66000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>64600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>63200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>65700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>62100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>61500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>63200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>64100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>62700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>62600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>63200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>64700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>63800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>57800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>56600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>55300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>55200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>51000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>50300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>54100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>51400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>48600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>48900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>50000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>49600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>40600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7785,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>242700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>328500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-87300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>121400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>272500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>333000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-62500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>161700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>262300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>349000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-25900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>92100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>347100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>112000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-70700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>328400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>209300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-31400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>159400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>329100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>177100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>149600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>265500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>155400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>164300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>272900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>57000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7923,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-53700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-54700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-82500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-124100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-31000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-33000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-78700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-50100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-29500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-18300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-37200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-30200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-24000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-69200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-52600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-45100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-33400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-65700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-47900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-34300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8213,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-51900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-15200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-71500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-134500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-92400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-30000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-185700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-39900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-28300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-36500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-29300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-20700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-69000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-376800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-43400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-148300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-63700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-340700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-18800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,41 +8351,43 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-78500</v>
+      </c>
+      <c r="F96" s="3">
         <v>-78700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-81600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-77000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-77000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-76900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-77500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-35700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-35600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -7930,55 +8398,61 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-70700</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-71000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-71100</v>
       </c>
       <c r="T96" s="3">
         <v>-71000</v>
       </c>
       <c r="U96" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="V96" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-70900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-59500</v>
       </c>
       <c r="Y96" s="3">
         <v>-59500</v>
       </c>
       <c r="Z96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8739,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-153600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-212500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-501800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-96700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-104600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-140500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-132000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-136000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-84700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-39700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-39000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>526000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-12700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>4900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>441200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-268300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>198400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>125100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-119600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-240900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>135900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>63200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-191800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>11300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>543400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="F101" s="3">
         <v>6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-18900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>2400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-4300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-6100</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>4600</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-3500</v>
       </c>
       <c r="AB101" s="3">
         <v>4600</v>
       </c>
       <c r="AC101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>85100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>167300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-345500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>118300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>75000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-295900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-60200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>224300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-97800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>44400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>839600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>70300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>352700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-9900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>32000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>49900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-110800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>26300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-32000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-67200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>88700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>29300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>54900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>34200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>38900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>MTN</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1283300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1078000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>258600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>269800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1238400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1101700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>279400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>267100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1176700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>906500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>175600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>204200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>889100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>684600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>131800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>77200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>694100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>924600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>267800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>244000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>958000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>849600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>220000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>211600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>844500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>734600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>220900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>209100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>794600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>725200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>178300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>536900</v>
+      </c>
+      <c r="E9" s="3">
         <v>541100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>292100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>272600</v>
       </c>
-      <c r="G9" s="3">
-        <v>527900</v>
-      </c>
       <c r="H9" s="3">
+        <v>527800</v>
+      </c>
+      <c r="I9" s="3">
         <v>588700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>276200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>240500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>475200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>417000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>209400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>218200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>355800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>333000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>172700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>129900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>329600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>456500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>271700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>240800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>410600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>415500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>230400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>214200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>355500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>355900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>218600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>408100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>420800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>233800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>746400</v>
+      </c>
+      <c r="E10" s="3">
         <v>536900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-33500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2800</v>
       </c>
-      <c r="G10" s="3">
-        <v>710500</v>
-      </c>
       <c r="H10" s="3">
+        <v>710600</v>
+      </c>
+      <c r="I10" s="3">
         <v>513000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>701500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>489500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-33800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-14000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>533300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>351600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-40900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-52700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>364500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>468100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-3900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>547400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>434100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>489000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>378700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>185700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>386500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>304400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1333,50 +1352,50 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>28400</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1393,8 +1412,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1408,8 +1427,8 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1417,109 +1436,115 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E15" s="3">
         <v>69400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>66700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>68800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>66000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>64600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>63200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>65700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>62100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>63200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>64100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>62700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>62600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>63200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>64700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>63800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>57800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>56600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>55300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>55200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>51000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>50300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>54100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>51400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>50000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>49600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>736700</v>
+      </c>
+      <c r="E17" s="3">
         <v>727400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>465600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>429900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>737900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>773700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>442800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>365300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>636300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>581400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>341200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>374600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>501400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>476900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>295700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>247300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>475900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>613900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>403300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>364600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>535400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>547700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>347600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>324600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>476500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>477000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>324600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>311700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>474600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>472900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>268800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>546700</v>
+      </c>
+      <c r="E18" s="3">
         <v>350600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-207000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-160100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>500500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>328000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-163400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-98200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>540400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>325100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-165600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-170400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>387700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>207700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-163900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-170100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>218200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>310700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-135500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-120600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>422600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>301900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-127600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-113000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>368000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>257600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>320000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>252300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>10700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>15900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E21" s="3">
         <v>427300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-140700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-82500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>575700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>403500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-101700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>605600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>385400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-101300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-108500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>457300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>276900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-96500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-101200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>275500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>374300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-75900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-60900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>476700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>358200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-77500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-64300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>413900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>319600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>370800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>303200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E22" s="3">
         <v>40600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>39100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>35400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>33400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>24500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>26100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>510700</v>
+      </c>
+      <c r="E23" s="3">
         <v>317300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-248200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-191500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>467500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>299200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-201600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-131200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>504800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>286000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-202400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-210900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>354200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>176400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-194500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-197800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>186300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>284300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-156400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-137700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>401900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>282000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-147100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>344200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>252300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>297500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>244500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E24" s="3">
         <v>87500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-65200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-56900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>124300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>79000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-58000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-21600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>118200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>52000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-59900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-65900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>76900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-37500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-39800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-46600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-45400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>93300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>64000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-36400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-46800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>71900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>68200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>84800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>381400</v>
+      </c>
+      <c r="E26" s="3">
         <v>229800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-183000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-134600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>343200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>220100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-143600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-109700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>386600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>233900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-142500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-144900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>277300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>149100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-157000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-158000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>159800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>217000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-109800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-92300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>308500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>218000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-110700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>272300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>184100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>196900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>159700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E27" s="3">
         <v>219300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-175500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-128600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>325000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>208700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-137000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-108700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>372600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>223400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-139300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-140800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>274600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>147800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-153800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-153600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>152500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>206400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-106500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-89500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>292100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>206300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-107800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-80100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>256300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>171100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>181100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>149200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2718,8 +2778,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2736,17 +2796,17 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E33" s="3">
         <v>219300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-175500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-128600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>325000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>208700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-137000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-108700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>372600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>223400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-139300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-140800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>274600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>147800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-153800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-153600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>152500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>206400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-106500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-89500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>292100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>206300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-107800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-83700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>256300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>235700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>181100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>149200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E35" s="3">
         <v>219300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-175500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-128600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>325000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>208700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-137000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-108700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>372600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>223400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-139300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-140800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>274600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>147800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-153800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-153600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>152500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>206400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-106500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-89500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>292100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>206300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-107800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-83700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>256300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>235700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>181100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>149200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>705400</v>
+      </c>
+      <c r="E41" s="3">
         <v>812200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>728900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>563000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>896100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1295300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1180900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1107400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1401200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1407000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1468400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1244000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1344700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1301000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>462200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>391000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>482700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>136300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>59600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>158600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>141000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>178100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>181600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>235500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>140400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>117400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>195800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>140900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>106800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,400 +3811,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E43" s="3">
         <v>138300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>105500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>381100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>351600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>160400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>118500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>383400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>267100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>167100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>345400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>208100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>117000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>208500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>106700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>105300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>87300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>270900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>273100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>87700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>74200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>230800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>220200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>85400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>84600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>186900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>174400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>80800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>59400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>107800</v>
+      </c>
+      <c r="E44" s="3">
         <v>134800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>157700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>132500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>103600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>122100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>139900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>108700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>92600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>104600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>103700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>80300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>73000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>86900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>100900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>101900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>101700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>113900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>127900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>96500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>84100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>103000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>115000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>85600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>79400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>97500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>108100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>84800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>77300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>93400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>112800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E45" s="3">
         <v>93500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>142400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>131500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>131100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>182400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>182300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>192000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>84500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>96800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>75900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>68600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>70000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>65600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>66200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>76800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>66000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>62800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>38500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>62600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>62700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>51100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>58700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>53400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1231200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1178800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1134500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1208100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1482400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1760100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1621700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1791500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1845400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1767400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1777900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1745600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1684800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1573500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>841600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>665100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>750900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>413800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>428300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>527900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>466900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>415300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>393000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>538700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>519700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>481000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>395700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>433100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>498700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>373700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>332400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4183,11 +4287,11 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>101700</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
@@ -4212,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2562200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2626000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2618200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2654100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2660300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2712400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2600900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2406100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2435700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2484300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2365600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2368200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2424600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2471000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2482200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2515300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2515700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2588100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2606700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1943500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1948700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1932800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1826000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1627200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1640700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1976000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2004000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1968500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2029700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2000600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2033700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1996100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2069000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2067600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2082200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2109800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2100200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2124800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2079900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2025300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2023800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1983300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2071400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2081600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1914400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1903400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1853000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1851200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1756300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1772500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>38800</v>
+        <v>39300</v>
       </c>
       <c r="E52" s="3">
         <v>38800</v>
       </c>
       <c r="F52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="G52" s="3">
         <v>55900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>56100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>51400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>39800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>40400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>41000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>40200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>42800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>43900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>44000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>142800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>142600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>146500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>146800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>148800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>152600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>155000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>151400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5808700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5847700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5760000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5947800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6199500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6565000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6280900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6318000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6397300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6369700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6290600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6251100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6276600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6165800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5390500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5244200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5289700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5113700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5157700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4426100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4361700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4244900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4215900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4065000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4075400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,129 +5099,133 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E57" s="3">
         <v>130800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>161600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>148500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>114200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>179200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>162400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>151300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>104100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>137900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>98300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>64400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>86300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>74600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>59700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>62100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>126800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>141700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>96400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>80200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>106200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>118600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>80800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>58200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>94700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>103500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>71600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>51300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>88800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>90800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E58" s="3">
         <v>69100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>69700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>69000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>67800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>63700</v>
       </c>
       <c r="K58" s="3">
         <v>63700</v>
@@ -5101,34 +5234,34 @@
         <v>63700</v>
       </c>
       <c r="M58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="N58" s="3">
         <v>114800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>114100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>113500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>112800</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>63700</v>
       </c>
       <c r="R58" s="3">
         <v>63700</v>
       </c>
       <c r="S58" s="3">
-        <v>63600</v>
+        <v>63700</v>
       </c>
       <c r="T58" s="3">
         <v>63600</v>
       </c>
       <c r="U58" s="3">
+        <v>63600</v>
+      </c>
+      <c r="V58" s="3">
         <v>63800</v>
-      </c>
-      <c r="V58" s="3">
-        <v>48500</v>
       </c>
       <c r="W58" s="3">
         <v>48500</v>
@@ -5140,10 +5273,10 @@
         <v>48500</v>
       </c>
       <c r="Z58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AA58" s="3">
         <v>38500</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>38400</v>
       </c>
       <c r="AB58" s="3">
         <v>38400</v>
@@ -5164,402 +5297,417 @@
         <v>38400</v>
       </c>
       <c r="AH58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AI58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>868800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1028800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1131600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>913000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>803200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1039100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1112500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>895800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>662000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>953400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1036500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>766000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>539200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>783400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>811900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>480100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>429700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>728000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>766000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>574200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>486100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>607100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>623300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>474400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>401100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>526400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>567600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>494600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>400700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>503600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>525900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1040700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1228800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1362800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1130700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>986400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1287900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1342700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1110900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>829900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1155000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1267800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>978400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>717100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>982500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>950200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>603500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>555400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>918400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>971500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>719100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>614900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>761800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>790400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>593600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>497800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>659500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>709600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>604600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>490400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>630800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>655000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2700300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2721600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2732000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2750700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2773700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2789800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2769700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2670300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2687500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2695600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2704600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2736200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2740000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2768000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2387900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2387100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2365400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1817100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2005100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1527700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1310900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1345300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1487000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1234300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1078000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>745800</v>
+      </c>
+      <c r="E62" s="3">
         <v>746600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>737000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>730700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>839800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>709800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>616700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>689400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>814800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>725400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>651700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>707400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>792900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>728900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>676700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>722000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>738600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>728000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>658800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>452400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>542700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>454800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>388700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>425400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>495500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>434200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>427300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>473200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>562000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>454400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>370500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4805200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5017800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5127000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4943800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4925500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5102400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5016000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4705600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4568000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4804200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4858100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4656500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4494400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4705100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4224400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3927500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3867500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3688200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3855300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2925500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2695400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2781600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2876300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2475600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2304800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E72" s="3">
         <v>760800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>619700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>873700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1081000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>837600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>705900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>895900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1081500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>786500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>598800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>773800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>914600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>639900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>492100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>645900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>799500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>717600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>582200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>759800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>920300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>699000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>551900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>726700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>869900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>673100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>480000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>551000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>650300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>511500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>394700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1003500</v>
+      </c>
+      <c r="E76" s="3">
         <v>829900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>633000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1003900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1273900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1462600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1264900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1612400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1829300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1565500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1432500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1594600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1782200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1460700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1166100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1316700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1422100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1425500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1302500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1500600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1666400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1463300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1339600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1589400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1770700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E81" s="3">
         <v>219300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-175500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-128600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>325000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>208700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-137000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-108700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>372600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>223400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-139300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-140800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>274600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>147800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-153800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-153600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>152500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>206400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-106500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-89500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>292100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>206300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-107800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-83700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>256300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>235700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>181100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>149200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E83" s="3">
         <v>69400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>66000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>63200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>65700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>62100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>63200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>62700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>57800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>56600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>55300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>55200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>51000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>54100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>51400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>49600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E89" s="3">
         <v>242700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>328500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-87300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>121400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>272500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>333000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-62500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>161700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>262300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>349000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>92100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>347100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>112000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-72000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-70700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>328400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>209300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-31400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>159400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>329100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>177100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>149600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>265500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>155400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>164300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>272900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>57000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-76900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-53400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-53700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-54700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-82500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-124100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-31000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-78700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-50100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-29500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-18300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-30200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-24000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-69200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-52600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-65700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-71600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-51900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-134500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-92400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-30000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-185700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-26300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-69000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-376800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-43400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-148300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-340700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,44 +8585,45 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-83800</v>
+      </c>
+      <c r="E96" s="3">
         <v>-78200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-78500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-78700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-81600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-77000</v>
       </c>
       <c r="I96" s="3">
         <v>-77000</v>
       </c>
       <c r="J96" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-76900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-77500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-35700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-35600</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -8404,25 +8637,25 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-70700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-71000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-71100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-71000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-70900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-59500</v>
       </c>
       <c r="Z96" s="3">
         <v>-59500</v>
@@ -8431,28 +8664,31 @@
         <v>-59500</v>
       </c>
       <c r="AB96" s="3">
-        <v>-42600</v>
+        <v>-59500</v>
       </c>
       <c r="AC96" s="3">
         <v>-42600</v>
       </c>
       <c r="AD96" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-182300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-97600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-153600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-212500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-501800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-96700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-104600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-140500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-132000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-136000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-39700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-39000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>526000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>441200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-268300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>198400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>125100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-119600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-240900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>135900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>63200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-191800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>11300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>543400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E101" s="3">
         <v>11700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-108600</v>
+      </c>
+      <c r="E102" s="3">
         <v>85100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>167300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-345500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>118300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>75000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-295900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-60200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>224300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-97800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>839600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>70300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-91000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>352700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>49900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-110800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>88700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>29300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>54900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>34200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>38900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>265400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1283300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1078000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>258600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>269800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1238400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1101700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>279400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>267100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1176700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>906500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>175600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>204200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>889100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>684600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>131800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>77200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>694100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>924600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>267800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>244000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>958000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>849600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>220000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>211600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>844500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>734600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>220900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>209100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>794600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>725200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>178300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E9" s="3">
         <v>536900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>541100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>292100</v>
       </c>
-      <c r="G9" s="3">
-        <v>272600</v>
-      </c>
       <c r="H9" s="3">
-        <v>527800</v>
+        <v>225500</v>
       </c>
       <c r="I9" s="3">
-        <v>588700</v>
+        <v>527900</v>
       </c>
       <c r="J9" s="3">
+        <v>589000</v>
+      </c>
+      <c r="K9" s="3">
         <v>276200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>240500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>475200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>417000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>209400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>218200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>355800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>333000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>172700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>129900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>329600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>456500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>271700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>240800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>410600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>415500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>230400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>214200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>355500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>355900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>218600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>408100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>420800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>233800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E10" s="3">
         <v>746400</v>
       </c>
-      <c r="E10" s="3">
-        <v>536900</v>
-      </c>
       <c r="F10" s="3">
+        <v>536800</v>
+      </c>
+      <c r="G10" s="3">
         <v>-33500</v>
       </c>
-      <c r="G10" s="3">
-        <v>-2800</v>
-      </c>
       <c r="H10" s="3">
+        <v>44300</v>
+      </c>
+      <c r="I10" s="3">
         <v>710600</v>
       </c>
-      <c r="I10" s="3">
-        <v>513000</v>
-      </c>
       <c r="J10" s="3">
+        <v>512800</v>
+      </c>
+      <c r="K10" s="3">
         <v>3200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>701500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>489500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-33800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-14000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>533300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>351600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-40900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-52700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>364500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>468100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-3900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>547400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>434100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>489000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>378700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>185700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>386500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>304400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,64 +1358,67 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>52100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>100</v>
-      </c>
-      <c r="H14" s="3">
-        <v>100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K14" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>28400</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1415,8 +1435,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1430,8 +1450,8 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1439,112 +1459,118 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E15" s="3">
         <v>68500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>66700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>68800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>64600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>62100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>61500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>63200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>64100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>62700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>62600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>63200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>64700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>63800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>57800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>56600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>55300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>55200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>51000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>50300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>54100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>51400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>48900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>50000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>49600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>40600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>736700</v>
+        <v>452800</v>
       </c>
       <c r="E17" s="3">
-        <v>727400</v>
+        <v>699600</v>
       </c>
       <c r="F17" s="3">
-        <v>465600</v>
+        <v>723200</v>
       </c>
       <c r="G17" s="3">
-        <v>429900</v>
+        <v>466800</v>
       </c>
       <c r="H17" s="3">
-        <v>737900</v>
+        <v>426700</v>
       </c>
       <c r="I17" s="3">
-        <v>773700</v>
+        <v>685800</v>
       </c>
       <c r="J17" s="3">
+        <v>771600</v>
+      </c>
+      <c r="K17" s="3">
         <v>442800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>365300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>636300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>581400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>341200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>374600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>501400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>476900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>295700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>247300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>475900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>613900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>403300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>364600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>535400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>547700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>347600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>324600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>476500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>477000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>324600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>311700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>474600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>472900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>268800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>546700</v>
+        <v>-187400</v>
       </c>
       <c r="E18" s="3">
-        <v>350600</v>
+        <v>583700</v>
       </c>
       <c r="F18" s="3">
-        <v>-207000</v>
+        <v>354700</v>
       </c>
       <c r="G18" s="3">
-        <v>-160100</v>
+        <v>-208200</v>
       </c>
       <c r="H18" s="3">
-        <v>500500</v>
+        <v>-156900</v>
       </c>
       <c r="I18" s="3">
-        <v>328000</v>
+        <v>552600</v>
       </c>
       <c r="J18" s="3">
+        <v>330200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-163400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-98200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>540400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>325100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-165600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-170400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>387700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>207700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-163900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-170100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>218200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>310700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-135500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-120600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>422600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>301900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-127600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-113000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>368000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>257600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>320000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>252300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3900</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>7300</v>
+        <v>1200</v>
       </c>
       <c r="F20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="L20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="O20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="R20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="S20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X20" s="3">
         <v>3100</v>
       </c>
-      <c r="L20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="N20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>5500</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>6500</v>
-      </c>
-      <c r="R20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>5700</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>3100</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>10700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>15900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>619000</v>
+        <v>-115800</v>
       </c>
       <c r="E21" s="3">
-        <v>427300</v>
+        <v>651000</v>
       </c>
       <c r="F21" s="3">
-        <v>-140700</v>
+        <v>426600</v>
       </c>
       <c r="G21" s="3">
-        <v>-82500</v>
+        <v>-145600</v>
       </c>
       <c r="H21" s="3">
-        <v>575700</v>
+        <v>-85300</v>
       </c>
       <c r="I21" s="3">
-        <v>403500</v>
+        <v>620000</v>
       </c>
       <c r="J21" s="3">
+        <v>398500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-101700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>605600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>385400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-101300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-108500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>457300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>276900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-96500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-101200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>275500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>374300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-75900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-60900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>476700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>358200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-77500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-64300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>413900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>319600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>370800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>303200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E22" s="3">
         <v>39900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>36100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>35100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>37400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>39100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>37800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>24500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>26100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>15600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-234700</v>
+      </c>
+      <c r="E23" s="3">
         <v>510700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>317300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-248200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-191500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>467500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>299200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-201600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-131200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>504800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>286000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-202400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-210900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>354200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>176400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-194500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-197800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>186300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>284300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-156400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-137700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>401900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>282000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-147100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>344200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>252300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>297500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>244500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="E24" s="3">
         <v>129300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>87500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-65200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-56900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>124300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>79000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-58000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-21600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>118200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>52000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-59900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-65900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>27200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-37500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-39800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>67300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-46600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-45400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>93300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>64000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-46800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>71900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>68200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>84800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-181900</v>
+      </c>
+      <c r="E26" s="3">
         <v>381400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>229800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-183000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-134600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>343200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>220100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-143600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-109700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>386600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>233900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-142500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-144900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>277300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>149100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-157000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-158000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>159800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>217000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-109800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-92300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>308500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>218000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-110700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>272300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>184100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>196900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>159700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-175400</v>
+      </c>
+      <c r="E27" s="3">
         <v>362000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>219300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-175500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-128600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>325000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>208700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-137000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-108700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>372600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>223400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-139300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-140800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>274600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>147800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-153800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-153600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>152500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>206400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-106500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-89500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>292100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>206300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-107800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-80100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>256300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>171100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>181100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>149200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2781,8 +2842,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2799,17 +2860,17 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3900</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-7300</v>
+        <v>-1200</v>
       </c>
       <c r="F32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="U32" s="3">
+        <v>7500</v>
+      </c>
+      <c r="V32" s="3">
+        <v>200</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="X32" s="3">
         <v>-3100</v>
       </c>
-      <c r="L32" s="3">
-        <v>500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="T32" s="3">
-        <v>7500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>8200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-175400</v>
+      </c>
+      <c r="E33" s="3">
         <v>362000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>219300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-175500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-128600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>325000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>208700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-137000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-108700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>372600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>223400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-139300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-140800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>274600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>147800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-153800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-153600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>152500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>206400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-106500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-89500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>292100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>206300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-107800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-83700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>256300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>235700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>181100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>149200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-175400</v>
+      </c>
+      <c r="E35" s="3">
         <v>362000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>219300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-175500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-128600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>325000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>208700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-137000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-108700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>372600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>223400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-139300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-140800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>274600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>147800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-153800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-153600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>152500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>206400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-106500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-89500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>292100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>206300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-107800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-83700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>256300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>235700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>181100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>149200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>322800</v>
+      </c>
+      <c r="E41" s="3">
         <v>705400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>812200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>728900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>563000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>896100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1295300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1180900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1107400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1401200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1407000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1468400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1244000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1344700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1301000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>462200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>391000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>482700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>108900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>59600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>158600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>141000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>178100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>181600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>235500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>140400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>117400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>195800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>140900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>106800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -3814,435 +3904,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>375800</v>
+      </c>
+      <c r="E43" s="3">
         <v>342900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>138300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>381100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>351600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>160400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>383400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>267100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>167100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>345400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>208100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>117000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>208500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>106700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>105300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>87300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>270900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>273100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>87700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>74200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>230800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>220200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>85400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>84600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>186900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>174400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>80800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>59400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E44" s="3">
         <v>107800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>134800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>157700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>132500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>103600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>139900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>108700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>92600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>104600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>103700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>80300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>73000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>100900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>101900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>101700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>113900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>127900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>96500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>84100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>103000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>115000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>85600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>79400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>97500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>108100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>84800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>77300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>93400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>112800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>75000</v>
+        <v>28000</v>
       </c>
       <c r="E45" s="3">
-        <v>93500</v>
+        <v>57300</v>
       </c>
       <c r="F45" s="3">
-        <v>142400</v>
+        <v>71100</v>
       </c>
       <c r="G45" s="3">
-        <v>131500</v>
+        <v>130900</v>
       </c>
       <c r="H45" s="3">
-        <v>131100</v>
+        <v>78200</v>
       </c>
       <c r="I45" s="3">
-        <v>182400</v>
+        <v>108600</v>
       </c>
       <c r="J45" s="3">
+        <v>158300</v>
+      </c>
+      <c r="K45" s="3">
         <v>182300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>192000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>84500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>88700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>96800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>75900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>68600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>70000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>65600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>66200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>67800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>76800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>50100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>66000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>62800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>44200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>38500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>62600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>62700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>44000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>51100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>58700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>53400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>911400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1231200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1178800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1134500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1208100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1482400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1760100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1621700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1791500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1845400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1767400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1777900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1745600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1684800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1573500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>841600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>665100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>750900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>413800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>428300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>527900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>466900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>415300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>393000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>538700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>519700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>481000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>395700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>433100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>498700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>373700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>332400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+        <v>2300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4290,11 +4395,11 @@
         <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>101700</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2562200</v>
+        <v>2679300</v>
       </c>
       <c r="E48" s="3">
-        <v>2626000</v>
+        <v>2475700</v>
       </c>
       <c r="F48" s="3">
-        <v>2618200</v>
+        <v>2539300</v>
       </c>
       <c r="G48" s="3">
-        <v>2654100</v>
+        <v>2531700</v>
       </c>
       <c r="H48" s="3">
-        <v>2660300</v>
+        <v>2563800</v>
       </c>
       <c r="I48" s="3">
-        <v>2712400</v>
+        <v>2570300</v>
       </c>
       <c r="J48" s="3">
+        <v>2622100</v>
+      </c>
+      <c r="K48" s="3">
         <v>2600900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2406100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2435700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2484300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2365600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2368200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2424600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2471000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2482200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2515300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2515700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2588100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2606700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1943500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1948700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1932800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1826000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1627200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1640700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1980500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1976000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2004000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1968500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2029700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2000600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2033700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1996100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2069000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2067600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2082200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2109800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2100200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2124800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2079900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2025300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2023800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1983300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2071400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2081600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1914400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1903400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1853000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1851200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1756300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1772500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>39300</v>
+        <v>125000</v>
       </c>
       <c r="E52" s="3">
-        <v>38800</v>
+        <v>125900</v>
       </c>
       <c r="F52" s="3">
-        <v>38800</v>
+        <v>125600</v>
       </c>
       <c r="G52" s="3">
-        <v>55900</v>
+        <v>111400</v>
       </c>
       <c r="H52" s="3">
-        <v>56100</v>
+        <v>128900</v>
       </c>
       <c r="I52" s="3">
-        <v>58700</v>
+        <v>129500</v>
       </c>
       <c r="J52" s="3">
+        <v>129800</v>
+      </c>
+      <c r="K52" s="3">
         <v>62200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>51400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>37300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>37100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>41400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>40100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>39800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>41000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>40200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>42800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>43900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>44000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>142800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>142600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>146500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>146800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>148800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>152600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>155000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>151400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5698400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5808700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5847700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5760000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5947800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6199500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6565000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6280900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6318000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6397300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6369700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6290600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6251100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6276600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6165800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5390500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5244200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5289700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5113700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5157700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4426100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4361700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4244900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4215900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4065000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4075400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,135 +5230,139 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E57" s="3">
         <v>103500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>130800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>161600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>148500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>114200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>179200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>162400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>151300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>104100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>137900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>98300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>64400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>74600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>59700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>62100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>126800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>141700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>96400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>80200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>106200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>118600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>80800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>58200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>94700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>103500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>71600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>51300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>88800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>90800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>68500</v>
+        <v>89800</v>
       </c>
       <c r="E58" s="3">
-        <v>69100</v>
+        <v>107700</v>
       </c>
       <c r="F58" s="3">
-        <v>69700</v>
+        <v>107900</v>
       </c>
       <c r="G58" s="3">
-        <v>69200</v>
+        <v>108000</v>
       </c>
       <c r="H58" s="3">
-        <v>69000</v>
+        <v>106100</v>
       </c>
       <c r="I58" s="3">
-        <v>69600</v>
+        <v>106000</v>
       </c>
       <c r="J58" s="3">
+        <v>106200</v>
+      </c>
+      <c r="K58" s="3">
         <v>67800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>63700</v>
       </c>
       <c r="L58" s="3">
         <v>63700</v>
@@ -5237,34 +5371,34 @@
         <v>63700</v>
       </c>
       <c r="N58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="O58" s="3">
         <v>114800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>114100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>113500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>112800</v>
-      </c>
-      <c r="R58" s="3">
-        <v>63700</v>
       </c>
       <c r="S58" s="3">
         <v>63700</v>
       </c>
       <c r="T58" s="3">
-        <v>63600</v>
+        <v>63700</v>
       </c>
       <c r="U58" s="3">
         <v>63600</v>
       </c>
       <c r="V58" s="3">
+        <v>63600</v>
+      </c>
+      <c r="W58" s="3">
         <v>63800</v>
-      </c>
-      <c r="W58" s="3">
-        <v>48500</v>
       </c>
       <c r="X58" s="3">
         <v>48500</v>
@@ -5276,10 +5410,10 @@
         <v>48500</v>
       </c>
       <c r="AA58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AB58" s="3">
         <v>38500</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>38400</v>
       </c>
       <c r="AC58" s="3">
         <v>38400</v>
@@ -5300,414 +5434,429 @@
         <v>38400</v>
       </c>
       <c r="AI58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>868800</v>
+        <v>675600</v>
       </c>
       <c r="E59" s="3">
-        <v>1028800</v>
+        <v>712100</v>
       </c>
       <c r="F59" s="3">
-        <v>1131600</v>
+        <v>860700</v>
       </c>
       <c r="G59" s="3">
-        <v>913000</v>
+        <v>1002200</v>
       </c>
       <c r="H59" s="3">
-        <v>803200</v>
+        <v>693900</v>
       </c>
       <c r="I59" s="3">
-        <v>1039100</v>
+        <v>660600</v>
       </c>
       <c r="J59" s="3">
+        <v>882100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1112500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>895800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>662000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>953400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1036500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>766000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>539200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>783400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>811900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>480100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>429700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>728000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>766000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>574200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>486100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>607100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>623300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>474400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>401100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>526400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>567600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>494600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>400700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>503600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>525900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1113300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1040700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1228800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1362800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1130700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>986400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1287900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1342700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1110900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>829900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1155000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1267800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>978400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>717100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>982500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>950200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>603500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>555400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>918400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>971500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>719100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>614900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>761800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>790400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>593600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>497800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>659500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>709600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>604600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>490400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>630800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>655000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2700300</v>
+        <v>2955100</v>
       </c>
       <c r="E61" s="3">
-        <v>2721600</v>
+        <v>2855100</v>
       </c>
       <c r="F61" s="3">
-        <v>2732000</v>
+        <v>2890300</v>
       </c>
       <c r="G61" s="3">
-        <v>2750700</v>
+        <v>2897500</v>
       </c>
       <c r="H61" s="3">
-        <v>2773700</v>
+        <v>2919000</v>
       </c>
       <c r="I61" s="3">
-        <v>2789800</v>
+        <v>2948100</v>
       </c>
       <c r="J61" s="3">
+        <v>2974100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2769700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2670300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2687500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2695600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2704600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2736200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2740000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2768000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2387900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2387100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2365400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1817100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2005100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1527700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1310900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1345300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1487000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1234300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1078000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>745800</v>
+        <v>311800</v>
       </c>
       <c r="E62" s="3">
-        <v>746600</v>
+        <v>306200</v>
       </c>
       <c r="F62" s="3">
-        <v>737000</v>
+        <v>291300</v>
       </c>
       <c r="G62" s="3">
-        <v>730700</v>
+        <v>285500</v>
       </c>
       <c r="H62" s="3">
-        <v>839800</v>
+        <v>286300</v>
       </c>
       <c r="I62" s="3">
-        <v>709800</v>
+        <v>264200</v>
       </c>
       <c r="J62" s="3">
+        <v>237500</v>
+      </c>
+      <c r="K62" s="3">
         <v>616700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>689400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>814800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>725400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>651700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>707400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>792900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>728900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>676700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>722000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>738600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>728000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>658800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>452400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>542700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>454800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>388700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>425400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>495500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>434200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>427300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>473200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>562000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>454400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>370500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4805200</v>
+        <v>4660000</v>
       </c>
       <c r="E66" s="3">
-        <v>5017800</v>
+        <v>4486700</v>
       </c>
       <c r="F66" s="3">
-        <v>5127000</v>
+        <v>4697000</v>
       </c>
       <c r="G66" s="3">
-        <v>4943800</v>
+        <v>4831800</v>
       </c>
       <c r="H66" s="3">
-        <v>4925500</v>
+        <v>4612100</v>
       </c>
       <c r="I66" s="3">
-        <v>5102400</v>
+        <v>4600000</v>
       </c>
       <c r="J66" s="3">
+        <v>4787600</v>
+      </c>
+      <c r="K66" s="3">
         <v>5016000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4705600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4568000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4804200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4858100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4656500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4494400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4705100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4224400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3927500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3867500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3688200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3855300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2925500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2695400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2781600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2876300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2475600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2304800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>780400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1039000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>760800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>619700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>873700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1081000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>837600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>705900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>895900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1081500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>786500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>598800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>773800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>914600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>639900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>492100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>645900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>799500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>717600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>582200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>759800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>920300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>699000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>551900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>726700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>869900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>673100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>480000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>551000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>650300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>511500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>394700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>723500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1003500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>829900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>633000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1003900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1273900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1462600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1264900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1612400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1829300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1565500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1432500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1594600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1782200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1460700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1166100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1316700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1422100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1425500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1302500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1500600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1666400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1463300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1339600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1589400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1770700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-175400</v>
+      </c>
+      <c r="E81" s="3">
         <v>362000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>219300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-175500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-128600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>325000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>208700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-137000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-108700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>372600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>223400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-139300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-140800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>274600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>147800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-153800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-153600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>152500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>206400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-106500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-89500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>292100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>206300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-107800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-83700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>256300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>235700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>181100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>149200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>68500</v>
+        <v>63700</v>
       </c>
       <c r="E83" s="3">
-        <v>69400</v>
+        <v>69100</v>
       </c>
       <c r="F83" s="3">
-        <v>66700</v>
+        <v>66000</v>
       </c>
       <c r="G83" s="3">
-        <v>68800</v>
+        <v>64600</v>
       </c>
       <c r="H83" s="3">
-        <v>69100</v>
+        <v>58000</v>
       </c>
       <c r="I83" s="3">
-        <v>66000</v>
+        <v>65700</v>
       </c>
       <c r="J83" s="3">
+        <v>62100</v>
+      </c>
+      <c r="K83" s="3">
         <v>64600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>62100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>61500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>63200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>62600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>57800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>56600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>55300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>55200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>51000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>54100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>50000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>49600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>40600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-94200</v>
+      </c>
+      <c r="E89" s="3">
         <v>109900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>242700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>328500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-87300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>121400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>272500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>333000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-62500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>161700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>262300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>349000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>92100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>347100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>112000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-72000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-70700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>328400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>209300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-31400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>159400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>329100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>177100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>149600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>265500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>155400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>164300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>272900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>57000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-76900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-53400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-54700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-82500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-33000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-78700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-50100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-29500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-30200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-69200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-52600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-65700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-150200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-51900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-71500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-134500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-92400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-185700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-29300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-69000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-376800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-43400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-148300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-63700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-340700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,47 +8819,48 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-83800</v>
+        <v>83200</v>
       </c>
       <c r="E96" s="3">
-        <v>-78200</v>
+        <v>83800</v>
       </c>
       <c r="F96" s="3">
-        <v>-78500</v>
+        <v>78200</v>
       </c>
       <c r="G96" s="3">
-        <v>-78700</v>
+        <v>78500</v>
       </c>
       <c r="H96" s="3">
-        <v>-81600</v>
+        <v>78700</v>
       </c>
       <c r="I96" s="3">
+        <v>81600</v>
+      </c>
+      <c r="J96" s="3">
+        <v>77000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-77000</v>
       </c>
-      <c r="J96" s="3">
-        <v>-77000</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-76900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-77500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-35700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-35600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -8640,25 +8874,25 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-70700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-71000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-71100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-71000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-70900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-59500</v>
       </c>
       <c r="AA96" s="3">
         <v>-59500</v>
@@ -8667,28 +8901,31 @@
         <v>-59500</v>
       </c>
       <c r="AC96" s="3">
-        <v>-42600</v>
+        <v>-59500</v>
       </c>
       <c r="AD96" s="3">
         <v>-42600</v>
       </c>
       <c r="AE96" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-141400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-182300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-153600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-212500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-501800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-96700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-104600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-140500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-132000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-136000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-84700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-39700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>526000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>441200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-268300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>198400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>125100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-119600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-240900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>135900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>63200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-191800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>11300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>543400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-11400</v>
+        <v>6200</v>
       </c>
       <c r="E101" s="3">
-        <v>11700</v>
+        <v>-5100</v>
       </c>
       <c r="F101" s="3">
-        <v>-13200</v>
+        <v>14000</v>
       </c>
       <c r="G101" s="3">
-        <v>6200</v>
+        <v>-18900</v>
       </c>
       <c r="H101" s="3">
-        <v>-5100</v>
+        <v>-500</v>
       </c>
       <c r="I101" s="3">
-        <v>14000</v>
+        <v>-400</v>
       </c>
       <c r="J101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-18900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-379800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-108600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>85100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>167300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-345500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>118300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>75000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-295900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>224300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-97800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>839600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>70300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-91000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>352700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>49900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-110800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>26300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>88700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>29300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>54900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>34200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>38900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>MTN</t>
   </si>
@@ -656,467 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1137200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>260300</v>
+      </c>
+      <c r="F8" s="3">
         <v>265400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1283300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1078000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>258600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>269800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1238400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1101700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>279400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>267100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1176700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>906500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>175600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>204200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>889100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>684600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>131800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>77200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>694100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>924600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>267800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>244000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>958000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>849600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>220000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>211600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>844500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>734600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>220900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>209100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>794600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>725200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>178300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>565400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>296700</v>
+      </c>
+      <c r="F9" s="3">
         <v>236100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>536900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>541100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>292100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>225500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>527900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>589000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>276200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>240500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>475200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>417000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>209400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>218200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>355800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>333000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>172700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>129900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>329600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>456500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>271700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>240800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>410600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>415500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>230400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>214200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>355500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>355900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>218600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>23400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>408100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>420800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>233800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>571900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="F10" s="3">
         <v>29300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>746400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>536800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-33500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>44300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>710600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>512800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>26600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>701500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>489500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-33800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>533300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>351600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-40900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-52700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>364500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>468100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-3900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>3200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>547400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>434100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-10400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>489000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>378700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>2300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>185700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>386500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>304400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1179,10 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1285,14 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,70 +1395,76 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F14" s="3">
         <v>11300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>37100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>3200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>52100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2600</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>13200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>28400</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1438,11 +1478,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1453,124 +1493,136 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>71600</v>
+      </c>
+      <c r="F15" s="3">
         <v>71900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>68500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>69400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>66700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>68800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>69100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>66000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>64600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>63200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>65700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>62100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>61500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>63200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>64100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>62700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>62600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>63200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>64700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>63800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>57800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>56600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>55300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>55200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>51000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>50300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>54100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>51400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>48600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>48900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>50000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>49600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1656,230 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>753000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>475200</v>
+      </c>
+      <c r="F17" s="3">
         <v>452800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>699600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>723200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>466800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>426700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>685800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>771600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>442800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>365300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>636300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>581400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>341200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>374600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>501400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>476900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>295700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>247300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>475900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>613900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>403300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>364600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>535400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>547700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>347600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>324600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>476500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>477000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>324600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>311700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>474600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>472900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>268800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>384200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-214900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-187400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>583700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>354700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-208200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-156900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>552600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>330200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-163400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-98200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>540400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>325100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-165600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-170400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>387700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>207700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-163900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-170100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>218200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>310700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-135500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-120600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>422600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>301900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-127600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-113000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>368000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>257600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>320000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>252300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1916,560 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>6500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>4900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-7500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>10700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>15900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>1300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>456700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-141400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-115800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>651000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>426600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-145600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-85300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>620000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>398500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-101700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-31900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>605600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>385400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-101300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>457300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>276900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-96500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-101200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>275500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>374300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-75900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-60900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>476700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>358200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-77500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-64300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>413900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>319600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>370800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>303200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F22" s="3">
         <v>40700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>39900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>40600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>40700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>40200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>39100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>38400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>35300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>36100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>35100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>37400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>39500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>39100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>39000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>37800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>35400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>33400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>24500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>26100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>22700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>20300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>19600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>21000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>18600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>16400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>15600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>16000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>15200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>9800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>23300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>9000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>344400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-239800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-234700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>510700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>317300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-248200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-191500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>467500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>299200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-201600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-131200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>504800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>286000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-202400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-210900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>354200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>176400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-194500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-197800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>186300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>284300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-156400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-137700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>401900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>282000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-147100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>344200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>252300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>297500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>244500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-52800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>129300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>87500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-65200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-56900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>124300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>79000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-58000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-21600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>118200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>52000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-59900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-65900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>76900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>27200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-37500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-39800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>26400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>67300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-46600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-45400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>93300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>64000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-36400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-46800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>71900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>68200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>100600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>84800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2572,234 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>258100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-181500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-181900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>381400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>229800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-183000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-134600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>343200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>220100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-143600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-109700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>386600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>233900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-142500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-144900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>277300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>149100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-157000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-158000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>159800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>217000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-109800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-92300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>308500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>218000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-110700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>272300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>184100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>196900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>159700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-172800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-175400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>362000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>219300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-175500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-128600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>325000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>208700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-137000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-108700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>372600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>223400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-139300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-140800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>274600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>147800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-153800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-153600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>152500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>206400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-106500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>292100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>206300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-107800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-80100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>256300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>171100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>181100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>149200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2902,14 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2845,11 +2967,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2863,20 +2985,20 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2890,8 +3012,14 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3122,14 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3232,234 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-6500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-4900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>7500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>8200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>6500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-172800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-175400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>362000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>219300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-175500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-128600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>325000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>208700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-137000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-108700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>372600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>223400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-139300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-140800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>274600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>147800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-153800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-153600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>152500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>206400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-106500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>292100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>206300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-107800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-83700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>256300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>235700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>181100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>149200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3562,239 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-172800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-175400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>362000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>219300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-175500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-128600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>325000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>208700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-137000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-108700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>372600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>223400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-139300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-140800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>274600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>147800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-153800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-153600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>152500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>206400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-106500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>292100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>206300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-107800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-83700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>256300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>235700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>181100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>149200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3831,10 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3871,120 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>488200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>403800</v>
+      </c>
+      <c r="F41" s="3">
         <v>322800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>705400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>812200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>728900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>563000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>896100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1295300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1180900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1107400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1401200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1407000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1468400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1244000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1344700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1301000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>462200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>391000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>482700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>126800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>136300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>108900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>59600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>158600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>141000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>178100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>181600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>235500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>140400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>117400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>195800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>140900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,17 +3992,17 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>6300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>9100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3907,454 +4087,484 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>130200</v>
+      </c>
+      <c r="F43" s="3">
         <v>375800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>342900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>138300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>105500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>381100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>351600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>160400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>118500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>383400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>267100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>167100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>109000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>345400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>208100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>117000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>208500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>106700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>100200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>105300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>87300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>270900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>273100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>87700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>74200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>230800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>220200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>85400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>84600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>186900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>174400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>80800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>59400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>152900</v>
+      </c>
+      <c r="F44" s="3">
         <v>119000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>107800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>134800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>157700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>132500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>103600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>122100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>139900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>108700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>92600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>104600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>103700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>80300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>73000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>86900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>100900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>101900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>101700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>113900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>127900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>96500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>84100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>103000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>115000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>85600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>79400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>97500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>108100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>84800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>77300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>93400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>112800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>76700</v>
+      </c>
+      <c r="F45" s="3">
         <v>28000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>57300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>71100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>130900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>78200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>108600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>158300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>182300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>192000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>84500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>88700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>96800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>75900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>58900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>68600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>70000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>65600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>66200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>67800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>76800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>51700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>50100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>66000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>62800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>44200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>38500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>62600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>62700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>44000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>51100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>58700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>53400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>844500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>853600</v>
+      </c>
+      <c r="F46" s="3">
         <v>911400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1231200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1178800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1134500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1208100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1482400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1760100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1621700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1791500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1845400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1767400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1777900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1745600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1684800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1573500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>841600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>665100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>750900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>413800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>428300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>527900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>466900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>415300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>393000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>538700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>519700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>481000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>395700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>433100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>498700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>373700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>332400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2300</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>13900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>17200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>19300</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4398,14 +4608,14 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>101700</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
@@ -4427,216 +4637,234 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2633400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2689300</v>
+      </c>
+      <c r="F48" s="3">
         <v>2679300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2475700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2539300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2531700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2563800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2570300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2622100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2600900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2406100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2435700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2484300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2365600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2368200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2424600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2471000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2482200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2515300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2515700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2588100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2606700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1943500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1948700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1932800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1826000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1627200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1640700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1919800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1971600</v>
+      </c>
+      <c r="F49" s="3">
         <v>1980500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1976000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2004000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1968500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2029700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2000600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2033700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1996100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2069000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2067600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2082200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2109800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2100200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2124800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2079900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2025300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2023800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1983300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2071400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2081600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1914400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1903400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1853000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1851200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1756300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1772500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4967,14 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +5077,124 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>127700</v>
+      </c>
+      <c r="F52" s="3">
         <v>125000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>125900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>125600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>111400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>128900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>129500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>129800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>62200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>51400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>48600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>35800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>37300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>37100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>42500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>41500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>41400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>40100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>39800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>40400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>41000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>40200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>42800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>43900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>44000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>142800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>142600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>146500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>146800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>148800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>152600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>155000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>151400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5297,124 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5531200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5642200</v>
+      </c>
+      <c r="F54" s="3">
         <v>5698400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5808700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5847700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5760000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5947800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6199500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>6565000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6280900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>6318000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6397300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6369700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6290600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6251100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>6276600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6165800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5390500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>5244200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>5289700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5113700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5157700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4426100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4361700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>4244900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>4215900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4065000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4075400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5451,10 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,180 +5491,188 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>141900</v>
+      </c>
+      <c r="F57" s="3">
         <v>141200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>103500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>130800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>161600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>148500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>114200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>179200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>162400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>151300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>104100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>137900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>116500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>98300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>64400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>86300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>74600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>59700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>62100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>126800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>141700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>96400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>80200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>106200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>118600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>80800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>58200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>94700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>103500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>71600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>51300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>88800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>90800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>618300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>91600</v>
+      </c>
+      <c r="F58" s="3">
         <v>89800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>107700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>107900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>108000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>106100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>106000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>106200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>67800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>63700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>63700</v>
       </c>
       <c r="N58" s="3">
         <v>63700</v>
       </c>
       <c r="O58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="P58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>114800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>114100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>113500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>112800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>63700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>63700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>63600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>63600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>63800</v>
-      </c>
-      <c r="X58" s="3">
-        <v>48500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>48500</v>
       </c>
       <c r="Z58" s="3">
         <v>48500</v>
@@ -5413,13 +5681,13 @@
         <v>48500</v>
       </c>
       <c r="AB58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AD58" s="3">
         <v>38500</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>38400</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>38400</v>
       </c>
       <c r="AE58" s="3">
         <v>38400</v>
@@ -5437,426 +5705,456 @@
         <v>38400</v>
       </c>
       <c r="AJ58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AL58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>890600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1039200</v>
+      </c>
+      <c r="F59" s="3">
         <v>675600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>712100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>860700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1002200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>693900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>660600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>882100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1112500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>895800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>662000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>953400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1036500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>766000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>539200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>783400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>811900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>480100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>429700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>728000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>766000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>574200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>486100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>607100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>623300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>474400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>401100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>526400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>567600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>494600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>400700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>503600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>525900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1786700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1363700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1113300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1040700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1228800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1362800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1130700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>986400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1287900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1342700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1110900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>829900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1155000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1267800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>978400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>717100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>982500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>950200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>603500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>555400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>918400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>971500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>719100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>614900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>761800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>790400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>593600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>497800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>659500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>709600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>604600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>490400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>630800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>655000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2348500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2943300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2955100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2855100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2890300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2897500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2919000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2948100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2974100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2769700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2670300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2687500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2695600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2704600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2736200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2740000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2768000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2387900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2387100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2365400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1817100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2005100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1527700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1310900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1345300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1487000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1234300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1078000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>301600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>310300</v>
+      </c>
+      <c r="F62" s="3">
         <v>311800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>306200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>291300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>285500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>286300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>264200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>237500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>616700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>689400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>814800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>725400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>651700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>707400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>792900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>728900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>676700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>722000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>738600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>728000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>658800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>452400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>542700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>454800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>388700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>425400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>495500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>434200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>427300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>473200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>562000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>454400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>370500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6257,14 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6367,14 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6477,124 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4715100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4896900</v>
+      </c>
+      <c r="F66" s="3">
         <v>4660000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4486700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4697000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4831800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4612100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4600000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4787600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5016000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4705600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4568000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4804200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4858100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4656500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4494400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4705100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4224400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3927500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3867500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3688200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3855300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2925500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>2695400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>2781600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>2876300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2475600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2304800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6631,10 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6737,14 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6847,14 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6957,14 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +7067,124 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>687200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>524500</v>
+      </c>
+      <c r="F72" s="3">
         <v>780400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1039000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>760800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>619700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>873700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1081000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>837600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>705900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>895900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1081500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>786500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>598800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>773800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>914600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>639900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>492100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>645900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>799500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>717600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>582200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>759800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>920300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>699000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>551900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>726700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>869900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>673100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>480000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>551000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>650300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>511500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>394700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7287,14 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7397,14 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7507,124 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>530700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>444100</v>
+      </c>
+      <c r="F76" s="3">
         <v>723500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1003500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>829900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>633000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1003900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1273900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1462600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1264900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1612400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1829300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1565500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1432500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1594600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1782200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1460700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1166100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1316700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1422100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1425500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1302500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1500600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1666400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1463300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1339600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1589400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1770700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7727,239 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>245500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-172800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-175400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>362000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>219300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-175500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-128600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>325000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>208700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-137000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-108700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>372600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>223400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-139300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-140800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>274600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>147800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-153800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-153600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>152500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>206400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-106500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>292100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>206300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-107800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-83700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>256300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>235700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>181100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>149200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7996,120 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>66700</v>
+      </c>
+      <c r="F83" s="3">
         <v>63700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>69100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>66000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>64600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>58000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>65700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>62100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>64600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>63200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>65700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>62100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>61500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>63200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>64100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>62700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>62600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>63200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>64700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>63800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>57800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>56600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>55300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>55200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>51000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>50300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>54100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>51400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>48600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>48900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>50000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>49600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8212,14 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8322,14 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8432,14 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8542,14 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8652,124 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>326300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>282400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-94200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>109900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>242700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>328500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-87300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>121400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>272500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>333000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-62500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>161700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>262300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>349000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>92100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>347100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>112000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-72000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-70700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>328400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>209300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>159400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>329100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>177100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-31700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>149600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>265500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>155400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>164300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>272900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>57000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8806,120 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-56100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-24800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-76900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-53400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-53700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-54700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-82500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-124100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-31000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-33000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-78700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-50100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-18300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-37200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-30200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-26600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-24000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-69200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-52600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-45100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-33400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-65700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-47900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +9022,14 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +9132,124 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-150200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-24800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-71600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>5600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-51900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-71500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-134500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-92400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-30000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-185700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-39900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-9300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-36500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-29300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-26300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-20700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-69000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-376800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-43400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-148300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-63700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-340700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,53 +9286,55 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>83100</v>
+      </c>
+      <c r="F96" s="3">
         <v>83200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>83800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>78200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>78500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>78700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>81600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>77000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-77000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-76900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-77500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-35700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-35600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8877,55 +9345,61 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-70700</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-71000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-71100</v>
       </c>
       <c r="X96" s="3">
         <v>-71000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-70900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-59500</v>
       </c>
       <c r="AC96" s="3">
         <v>-59500</v>
       </c>
       <c r="AD96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9502,14 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9612,14 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9722,340 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-170400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-132300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-141400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-182300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-97600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-153600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-212500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-501800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-96700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-104600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-140500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-132000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-136000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-84700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-39700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-39000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>526000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-12700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>441200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-268300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>198400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>125100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-119600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>135900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>63200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-191800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>11300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>543400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="F101" s="3">
         <v>6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-18900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-18900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>2900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-6100</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>4600</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-3500</v>
       </c>
       <c r="AF101" s="3">
         <v>4600</v>
       </c>
       <c r="AG101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>81400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-379800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-108600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>85100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>167300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-345500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>118300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>75000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-295900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-60200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>224300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-97800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>44400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>839600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>70300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-91000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>352700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>32000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>49900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-110800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>26300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>88700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>29300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>54900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>34200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>38900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>MTN</t>
   </si>
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1295600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1137200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>260300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>265400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1283300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1078000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>258600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>269800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1238400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1101700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>279400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>267100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1176700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>906500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>175600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>204200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>889100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>684600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>131800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>77200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>694100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>924600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>267800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>244000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>958000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>849600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>220000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>211600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>844500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>734600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>220900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>209100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>794600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>725200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>178300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E9" s="3">
         <v>565400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>296700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>236100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>536900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>541100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>292100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>225500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>527900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>589000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>276200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>240500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>475200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>417000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>209400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>218200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>355800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>333000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>172700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>129900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>329600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>456500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>271700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>240800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>410600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>415500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>230400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>214200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>355500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>355900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>218600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>408100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>420800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>233800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>751500</v>
+      </c>
+      <c r="E10" s="3">
         <v>571900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-36400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>746400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>536800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-33500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>710600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>512800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>701500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>489500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-33800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-14000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>533300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>351600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-40900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-52700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>364500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>468100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>547400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>434100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-10400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>489000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>378700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>185700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>386500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>304400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,73 +1417,76 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-12900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>37100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>52100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>28400</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1484,8 +1503,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1499,8 +1518,8 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1508,121 +1527,127 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E15" s="3">
         <v>73100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>68500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>69100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>64600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>63200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>65700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>62100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>61500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>63200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>64100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>62700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>62600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>63200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>64700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>63800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>57800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>56600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>55300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>55200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>51000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>50300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>54100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>51400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>48600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>48900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>50000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>49600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>40600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>724700</v>
+      </c>
+      <c r="E17" s="3">
         <v>753000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>475200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>452800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>699600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>723200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>466800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>426700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>685800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>771600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>442800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>365300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>636300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>581400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>341200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>374600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>501400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>476900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>295700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>247300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>475900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>613900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>403300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>364600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>535400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>547700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>347600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>324600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>476500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>477000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>324600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>311700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>474600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>472900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>268800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>570900</v>
+      </c>
+      <c r="E18" s="3">
         <v>384200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-214900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-187400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>583700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>354700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-208200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-156900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>552600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>330200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-163400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-98200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>540400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>325100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-165600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-170400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>387700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>207700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-163900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-170100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>218200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>310700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-135500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-120600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>422600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>301900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-127600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-113000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>368000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>257600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>320000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>252300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>15900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>647900</v>
+      </c>
+      <c r="E21" s="3">
         <v>456700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-141400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-115800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>651000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>426600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-145600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-85300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>620000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>398500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-101700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>605600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>385400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-101300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-108500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>457300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>276900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-96500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-101200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>275500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>374300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-75900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-60900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>476700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>358200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-77500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-64300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>413900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>319600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>370800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>303200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E22" s="3">
         <v>42400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>39900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>40700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>35300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>36100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>37400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>39100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>39000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>35400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>33400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>26100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>18600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>15600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>15200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>12000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>545400</v>
+      </c>
+      <c r="E23" s="3">
         <v>344400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-239800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-234700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>510700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>317300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-248200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-191500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>467500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>299200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-201600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-131200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>504800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>286000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-202400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-210900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>354200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>176400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-194500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-197800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>186300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>284300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-156400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-137700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>401900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>282000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-147100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>344200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>252300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>297500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>244500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E24" s="3">
         <v>86300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-58200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-52800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>129300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>87500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-65200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-56900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>124300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>79000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-58000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-21600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>118200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>52000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-59900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-65900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>76900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>27200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-37500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-39800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>67300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-46600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-45400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>93300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>64000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-36400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-46800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>71900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>68200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>100600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>84800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>414300</v>
+      </c>
+      <c r="E26" s="3">
         <v>258100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-181500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-181900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>381400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>229800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-183000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-134600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>343200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>220100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-143600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-109700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>386600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>233900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-142500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-144900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>277300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>149100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-157000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-158000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>159800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>217000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-109800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-92300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>308500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>218000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-110700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>272300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>184100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>196900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>159700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E27" s="3">
         <v>245500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-172800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-175400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>362000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>219300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-175500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-128600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>325000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>208700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-137000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-108700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>372600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>223400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-139300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-140800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>274600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>147800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-153800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-153600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>152500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>206400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>292100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>206300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-107800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-80100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>256300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>171100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>181100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>149200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2973,8 +3033,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2991,17 +3051,17 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>6500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E33" s="3">
         <v>245500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-172800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-175400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>362000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>219300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-175500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-128600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>325000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>208700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-137000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-108700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>372600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>223400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-139300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-140800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>274600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>147800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-153800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-153600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>152500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>206400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>292100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>206300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-107800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-83700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>256300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>235700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>181100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>149200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E35" s="3">
         <v>245500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-172800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-175400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>362000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>219300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-175500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-128600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>325000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>208700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-137000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-108700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>372600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>223400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-139300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-140800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>274600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>147800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-153800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-153600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>152500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>206400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>292100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>206300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-107800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-83700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>256300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>235700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>181100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>149200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>467000</v>
+      </c>
+      <c r="E41" s="3">
         <v>488200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>403800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>322800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>705400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>812200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>728900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>563000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>896100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1295300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1180900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1107400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1401200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1407000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1468400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1244000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1344700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1301000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>462200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>391000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>482700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>126800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>136300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>108900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>59600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>158600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>141000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>178100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>181600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>235500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>140400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>117400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>195800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>140900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>106800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3998,14 +4087,14 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>6300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -4093,448 +4182,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E43" s="3">
         <v>123600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>130200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>375800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>342900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>138300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>381100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>351600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>160400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>118500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>383400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>267100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>167100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>345400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>208100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>117000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>208500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>106700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>105300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>87300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>270900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>273100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>87700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>74200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>230800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>220200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>85400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>84600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>186900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>174400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>80800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>59400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E44" s="3">
         <v>132000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>152900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>119000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>107800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>134800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>157700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>132500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>103600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>139900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>108700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>92600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>104600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>103700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>80300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>73000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>86900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>100900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>101900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>101700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>113900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>127900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>96500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>84100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>103000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>115000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>85600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>79400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>97500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>108100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>84800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>77300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>93400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>112800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E45" s="3">
         <v>27400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>76700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>57300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>71100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>130900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>78200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>108600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>158300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>182300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>192000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>84500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>88700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>96800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>75900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>58900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>68600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>65600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>66200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>67800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>76800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>51700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>50100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>66000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>62800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>38500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>62600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>62700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>44000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>58700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>53400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1003900</v>
+      </c>
+      <c r="E46" s="3">
         <v>844500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>853600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>911400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1231200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1178800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1134500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1208100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1482400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1760100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1621700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1791500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1845400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1767400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1777900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1745600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1684800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1573500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>841600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>665100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>750900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>413800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>428300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>527900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>466900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>415300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>393000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>538700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>519700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>481000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>395700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>433100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>498700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>373700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>332400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4544,30 +4648,30 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>2300</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>13900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19300</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4614,11 +4718,11 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>101700</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
@@ -4643,228 +4747,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2640600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2633400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2689300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2679300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2475700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2539300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2531700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2563800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2570300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2622100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2600900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2406100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2435700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2484300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2365600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2368200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2424600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2471000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2482200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2515300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2515700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2588100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2606700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1943500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1948700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1932800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1826000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1627200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1640700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1979000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1919800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1971600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1980500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1976000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2004000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1968500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2029700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2000600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2033700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1996100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2069000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2067600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2082200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2109800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2100200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2124800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2079900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2025300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2023800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1983300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2071400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2081600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1914400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1903400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1853000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1851200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1756300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1772500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E52" s="3">
         <v>133600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>127700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>125000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>125900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>125600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>111400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>128900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>129500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>129800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>48600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>37300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>42500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>41400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>40100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>39800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>40400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>41000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>40200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>42800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>43900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>44000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>142800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>142600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>146500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>146800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>148800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>152600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>155000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>151400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5763000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5531200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5642200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5698400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5808700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5847700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5760000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5947800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6199500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6565000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6280900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6318000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6397300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6369700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6290600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6251100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6276600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6165800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5390500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5244200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5289700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5113700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5157700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4426100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4361700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4244900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4215900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4065000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4075400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,153 +5622,157 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E57" s="3">
         <v>138200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>141900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>141200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>103500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>130800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>161600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>114200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>179200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>162400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>151300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>104100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>137900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>116500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>98300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>64400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>86300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>74600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>59700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>62100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>126800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>141700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>96400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>80200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>106200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>118600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>80800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>58200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>94700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>103500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>71600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>51300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>88800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>90800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>625500</v>
+      </c>
+      <c r="E58" s="3">
         <v>618300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>91600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>89800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>107700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>107900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>108000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>106100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>106000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>106200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>67800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>63700</v>
       </c>
       <c r="O58" s="3">
         <v>63700</v>
@@ -5648,34 +5781,34 @@
         <v>63700</v>
       </c>
       <c r="Q58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="R58" s="3">
         <v>114800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>114100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>113500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>112800</v>
-      </c>
-      <c r="U58" s="3">
-        <v>63700</v>
       </c>
       <c r="V58" s="3">
         <v>63700</v>
       </c>
       <c r="W58" s="3">
-        <v>63600</v>
+        <v>63700</v>
       </c>
       <c r="X58" s="3">
         <v>63600</v>
       </c>
       <c r="Y58" s="3">
+        <v>63600</v>
+      </c>
+      <c r="Z58" s="3">
         <v>63800</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>48500</v>
       </c>
       <c r="AA58" s="3">
         <v>48500</v>
@@ -5687,10 +5820,10 @@
         <v>48500</v>
       </c>
       <c r="AD58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AE58" s="3">
         <v>38500</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>38400</v>
       </c>
       <c r="AF58" s="3">
         <v>38400</v>
@@ -5711,450 +5844,465 @@
         <v>38400</v>
       </c>
       <c r="AL58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AM58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>742100</v>
+      </c>
+      <c r="E59" s="3">
         <v>890600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1039200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>675600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>712100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>860700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1002200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>693900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>660600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>882100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1112500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>895800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>662000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>953400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1036500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>766000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>539200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>783400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>811900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>480100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>429700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>728000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>766000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>574200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>486100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>607100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>623300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>474400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>401100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>526400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>567600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>494600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>400700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>503600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>525900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1632600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1786700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1363700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1113300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1040700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1228800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1362800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1130700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>986400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1287900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1342700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1110900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>829900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1155000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1267800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>978400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>717100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>982500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>950200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>603500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>555400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>918400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>971500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>719100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>614900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>761800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>790400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>593600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>497800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>659500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>709600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>604600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>490400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>630800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>655000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2326700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2348500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2943300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2955100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2855100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2890300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2897500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2919000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2948100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2974100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2769700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2670300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2687500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2695600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2704600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2736200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2740000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2768000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2387900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2387100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2365400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1817100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2005100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1527700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1310900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1345300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1487000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1234300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1078000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E62" s="3">
         <v>301600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>310300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>311800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>306200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>291300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>285500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>286300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>264200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>237500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>616700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>689400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>814800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>725400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>651700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>707400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>792900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>728900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>676700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>722000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>738600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>728000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>658800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>452400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>542700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>454800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>388700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>425400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>495500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>434200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>427300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>473200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>562000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>454400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>370500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4527100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4715100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4896900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4660000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4486700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4697000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4831800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4612100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4600000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4787600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5016000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4705600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4568000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4804200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4858100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4656500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4494400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4705100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4224400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3927500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3867500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3688200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3855300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2925500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2695400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2781600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2876300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2475600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2304800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>997400</v>
+      </c>
+      <c r="E72" s="3">
         <v>687200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>524500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>780400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1039000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>760800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>619700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>873700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1081000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>837600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>705900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>895900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1081500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>786500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>598800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>773800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>914600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>639900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>492100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>645900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>799500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>717600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>582200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>759800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>920300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>699000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>551900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>726700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>869900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>673100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>480000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>551000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>650300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>511500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>394700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>895400</v>
+      </c>
+      <c r="E76" s="3">
         <v>530700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>444100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>723500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1003500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>829900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>633000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1003900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1273900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1462600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1264900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1612400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1829300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1565500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1432500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1594600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1782200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1460700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1166100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1316700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1422100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1425500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1302500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1500600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1666400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1463300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1339600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1589400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1770700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E81" s="3">
         <v>245500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-172800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-175400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>362000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>219300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-175500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-128600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>325000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>208700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-137000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-108700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>372600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>223400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-139300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-140800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>274600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>147800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-153800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-153600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>152500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>206400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-106500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>292100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>206300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-107800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-83700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>256300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>235700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>181100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>149200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E83" s="3">
         <v>69400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>66700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>66000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>58000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>65700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>62100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>64600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>63200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>62100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>62700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>62600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>63200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>55300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>55200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>54100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>48600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>50000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>49600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>40600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E89" s="3">
         <v>326300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>282400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-94200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>109900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>242700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>328500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-87300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>121400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>272500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>333000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>161700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>262300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>349000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>92100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>347100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>112000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-72000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-70700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>328400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>209300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>159400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>329100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>177100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>149600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>265500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>155400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>164300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>272900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>57000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-75000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-53700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-82500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-124100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-31000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-33000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-78700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-50100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-29500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-18300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-30200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-45100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-65700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-47900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-150200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-51900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-92400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-30000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-185700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-36500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-29300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-26300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-376800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-148300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-63700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-340700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,56 +9520,57 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E96" s="3">
         <v>82800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>83100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>83200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>83800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>78200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>78500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>78700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>81600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>77000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-77000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-76900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-77500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -9351,25 +9584,25 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-70700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-71100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-59500</v>
       </c>
       <c r="AD96" s="3">
         <v>-59500</v>
@@ -9378,28 +9611,31 @@
         <v>-59500</v>
       </c>
       <c r="AF96" s="3">
-        <v>-42600</v>
+        <v>-59500</v>
       </c>
       <c r="AG96" s="3">
         <v>-42600</v>
       </c>
       <c r="AH96" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-134800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-170400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-132300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-141400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-182300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-97600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-153600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-212500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-501800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-96700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-104600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-140500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-132000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-136000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-84700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-39700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-39000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>526000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>441200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-268300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>198400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>125100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-119600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>135900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>63200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-191800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>11300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>543400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E101" s="3">
         <v>11700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>14000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E102" s="3">
         <v>86100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>81400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-379800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-108600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>85100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>167300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-345500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>118300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>75000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-295900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>224300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-97800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>839600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>70300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-91000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>352700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>49900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-110800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>26300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>88700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>29300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>54900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>34200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>38900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>MTN</t>
   </si>
@@ -656,518 +656,544 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1083900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>271000</v>
+      </c>
+      <c r="F8" s="3">
         <v>271300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1295600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1137200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>260300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>265400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1283300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1078000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>258600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>269800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1238400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1101700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>279400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>267100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1176700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>906500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>175600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>204200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>889100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>684600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>131800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>77200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>694100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>924600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>267800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>244000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>958000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>849600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>220000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>211600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>844500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>734600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>220900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>209100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>794600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>725200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>178300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>179900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>541500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>302900</v>
+      </c>
+      <c r="F9" s="3">
         <v>242100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>544000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>565400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>296700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>236100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>536900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>541100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>292100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>225500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>527900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>589000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>276200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>240500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>475200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>417000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>209400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>218200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>355800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>333000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>172700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>129900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>329600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>456500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>271700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>240800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>410600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>415500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>230400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>214200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>355500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>355900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>218600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>23400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>408100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>420800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>233800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>229900</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="F10" s="3">
         <v>29200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>751500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>571900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-36400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>29300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>746400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>536800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-33500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>44300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>710600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>512800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>26600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>701500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>489500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>-33800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-14000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>533300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>351600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-40900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-52700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>364500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>468100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>547400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>434100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>489000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>378700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>185700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>386500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>304400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>-55500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>-50000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1234,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1352,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,82 +1474,88 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F14" s="3">
         <v>8200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-10300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-12900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>11300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>37100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>3200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>52100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>2100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>3600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>2600</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>13200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>28400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1529,11 +1569,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1544,136 +1584,148 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>73100</v>
+      </c>
+      <c r="F15" s="3">
         <v>77100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>74600</v>
       </c>
-      <c r="F15" s="3">
-        <v>73100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>71600</v>
-      </c>
       <c r="H15" s="3">
+        <v>74400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J15" s="3">
         <v>74500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>68500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>69400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>66700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>68800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>69100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>66000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>64600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>63200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>65700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>62100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>61500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>63200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>64100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>62700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>62600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>63200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>64700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>63800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>57800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>56600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>55300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>55200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>51000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>50300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>54100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>51400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>48600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>48900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>50000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>49600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AO15" s="3">
         <v>40600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AP15" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1763,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>737500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>486500</v>
+      </c>
+      <c r="F17" s="3">
         <v>466700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>724700</v>
       </c>
-      <c r="F17" s="3">
-        <v>753000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>475200</v>
-      </c>
       <c r="H17" s="3">
+        <v>754200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>475100</v>
+      </c>
+      <c r="J17" s="3">
         <v>455400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>699600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>723200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>466800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>426700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>685800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>771600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>442800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>365300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>636300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>581400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>341200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>374600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>501400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>476900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>295700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>247300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>475900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>613900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>403300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>364600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>535400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>547700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>347600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>324600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>476500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>477000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>324600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>311700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>474600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>472900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>268800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>273700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>346500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-215400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-195400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>570900</v>
       </c>
-      <c r="F18" s="3">
-        <v>384200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-214900</v>
-      </c>
       <c r="H18" s="3">
+        <v>383000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-214800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-190000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>583700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>354700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-208200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-156900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>552600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>330200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-163400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>540400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>325100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-165600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-170400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>387700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>207700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-163900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-170100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>218200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>310700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-135500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-120600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>422600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>301900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-127600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-113000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>368000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>257600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-103700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>320000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>252300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-90500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-93800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2051,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>5500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>6500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>4900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>5700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>10700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>15900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>1300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>5300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>419900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-141300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-118000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>647900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>456700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-141400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-115800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>651000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>426600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-145600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-85300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>620000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>398500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-101700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>605600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>385400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-101300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-108500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>457300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>276900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-96500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-101200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>275500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>374300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-75900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-60900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>476700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>358200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-77500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-64300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>413900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>319600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-61500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-37800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>370800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>303200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>-44600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-52500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>51300</v>
+      </c>
+      <c r="F22" s="3">
         <v>45800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>41300</v>
       </c>
-      <c r="F22" s="3">
-        <v>42400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>42200</v>
-      </c>
       <c r="H22" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I22" s="3">
+        <v>42800</v>
+      </c>
+      <c r="J22" s="3">
         <v>43400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>39900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>40600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>40700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>40200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>39100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>38400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>35300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>36100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>35100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>37400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>39500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>39100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>39000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>37800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>35400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>33400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>24500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>26100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>22700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>20300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>19600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>21000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>18600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>16400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>15600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>16000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>9800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>23300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>9000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AO22" s="3">
         <v>12000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AP22" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>298100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-257100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-247600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>545400</v>
       </c>
-      <c r="F23" s="3">
-        <v>344400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-239800</v>
-      </c>
       <c r="H23" s="3">
+        <v>342900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-240300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-240000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>510700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>317300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-248200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-191500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>467500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>299200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-201600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-131200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>504800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>286000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-202400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-210900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>354200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>176400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-194500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-197800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>186300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>284300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-156400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-137700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>401900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>282000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-147100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-131000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>344200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>252300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-125300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-96500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>297500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>244500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-97100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-103700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-54700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>131000</v>
       </c>
-      <c r="F24" s="3">
-        <v>86300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-58200</v>
-      </c>
       <c r="H24" s="3">
+        <v>86000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="J24" s="3">
         <v>-58800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>129300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>87500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-65200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-56900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>124300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>79000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-58000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>118200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>52000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-59900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-65900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>76900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>27200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-37500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>26400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>67300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-46600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-45400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>93300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>64000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-36400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-46800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>71900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>68200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>-93400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>100600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>84800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>-33500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>-38400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2779,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>225800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-196500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-192900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>414300</v>
       </c>
-      <c r="F26" s="3">
-        <v>258100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-181500</v>
-      </c>
       <c r="H26" s="3">
+        <v>256900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-182000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-181200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>381400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>229800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-183000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-134600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>343200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>220100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-143600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-109700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>386600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>233900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-142500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-144900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>277300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>149100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-157000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-158000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>159800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>217000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-109800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-92300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>308500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>218000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-110700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>272300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>184100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-31900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-61200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>196900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>159700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-63600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-186800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-185500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>392800</v>
       </c>
-      <c r="F27" s="3">
-        <v>245500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-172800</v>
-      </c>
       <c r="H27" s="3">
+        <v>244400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-173300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-174700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>362000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>219300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-175500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-128600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>325000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>208700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-137000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-108700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>372600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>223400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-139300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-140800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>274600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>147800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-153800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-153600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>152500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>206400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>292100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>206300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-107800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-80100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>256300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>171100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-28400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-57100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>181100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>149200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-62600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3145,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3100,11 +3222,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3118,20 +3240,20 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>64600</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3145,8 +3267,14 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3389,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3511,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-5500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-6500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-4900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>7500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>8200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-15900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-186800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-185500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>392800</v>
       </c>
-      <c r="F33" s="3">
-        <v>245500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-172800</v>
-      </c>
       <c r="H33" s="3">
+        <v>244400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-173300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-174700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>362000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>219300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-175500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-128600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>325000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>208700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-137000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-108700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>372600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>223400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-139300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-140800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>274600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>147800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-153800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-153600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>152500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>206400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>292100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>206300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-107800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-83700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>256300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>235700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-28400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-57100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>181100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>149200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-62600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3877,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-186800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-185500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>392800</v>
       </c>
-      <c r="F35" s="3">
-        <v>245500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-172800</v>
-      </c>
       <c r="H35" s="3">
+        <v>244400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-173300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-174700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>362000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>219300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-175500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-128600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>325000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>208700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-137000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-108700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>372600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>223400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-139300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-140800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>274600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>147800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-153800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-153600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>152500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>206400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>292100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>206300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-107800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-83700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>256300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>235700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-28400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-57100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>181100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>149200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-62600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4174,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4218,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>384700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>581500</v>
+      </c>
+      <c r="F41" s="3">
         <v>440300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>467000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>488200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>403800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>322800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>705400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>812200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>728900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>563000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>896100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1295300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1180900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1107400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1401200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1407000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1468400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1244000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1344700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1301000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>462200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>391000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>482700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>126800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>136300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>108900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>59600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>158600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>141000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>178100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>181600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>235500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>140400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>117400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>195800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>140900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>106800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>67900</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4183,17 +4363,17 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>6300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>9100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4278,472 +4458,502 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>175800</v>
+      </c>
+      <c r="F43" s="3">
         <v>382400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>335900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>123600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>130200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>375800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>342900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>138300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>105500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>381100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>351600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>160400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>118500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>383400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>267100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>167100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>109000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>345400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>208100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>117000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>208500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>106700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>100200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>105300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>87300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>270900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>273100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>87700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>74200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>230800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>220200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>85400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>84600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>186900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>174400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>80800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>59400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>147100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>141400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>154400</v>
+      </c>
+      <c r="F44" s="3">
         <v>117200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>114600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>132000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>152900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>119000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>107800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>134800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>157700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>132500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>103600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>122100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>139900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>108700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>92600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>104600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>103700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>80300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>73000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>86900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>100900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>101900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>101700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>113900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>127900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>96500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>84100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>103000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>115000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>85600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>79400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>97500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>108100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>84800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>77300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>93400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>112800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>38800</v>
+      </c>
+      <c r="F45" s="3">
         <v>35700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>33700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>27400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>76700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>18600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>57300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>71100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>130900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>78200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>108600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>158300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>182300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>192000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>84500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>88700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>96800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>75900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>58900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>68600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>70000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>65600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>66200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>67800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>76800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>51700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>50100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>66000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>62800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>44200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>38500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>62600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>62700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>44000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>51100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>58700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>53400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>822700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1047600</v>
+      </c>
+      <c r="F46" s="3">
         <v>1049800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1003900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>844500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>853600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>902000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1231200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1178800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1134500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1208100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1482400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1760100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1621700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1791500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1845400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1767400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1777900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1745600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1684800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1573500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>841600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>665100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>750900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>413800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>428300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>527900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>466900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>415300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>393000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>538700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>519700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>481000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>395700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>433100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>498700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>373700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>332400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>322900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4768,24 +4978,24 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>13900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>17200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>16700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>19300</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4829,14 +5039,14 @@
         <v>0</v>
       </c>
       <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>101700</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
       <c r="AH47" s="3">
         <v>0</v>
       </c>
@@ -4858,240 +5068,258 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2650800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2616900</v>
+      </c>
+      <c r="F48" s="3">
         <v>2617100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2640600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2633400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2689300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2676800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2475700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2539300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2531700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2563800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2570300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2622100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2600900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2406100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2435700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2484300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2365600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2368200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2424600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2471000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>2482200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2515300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2515700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2588100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>2606700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1943500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1948700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1932800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>1826000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>1627200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>1640700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>1702200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>1714200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>1647000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>1694700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>1699100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>1363800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1998200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1960600</v>
+      </c>
+      <c r="F49" s="3">
         <v>1973700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1979000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1919800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1971600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1980500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1976000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2004000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1968500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2029700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2000600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2033700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1996100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2069000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2067600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2082200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>2109800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2100200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2124800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2079900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2025300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2023800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1983300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2071400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2081600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>1914400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>1903400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>1853000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>1851200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>1756300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>1772500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>1827100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>1771400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>1814700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>1710500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>1759000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>1741300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>649000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5434,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5556,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>138700</v>
+      </c>
+      <c r="F52" s="3">
         <v>137200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>139700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>133600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>127700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>127300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>125900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>125600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>111400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>128900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>129500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>129800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>62200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>51400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>48600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>35800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>37300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>37100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>42500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>41500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>41400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>40100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>39800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>40400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>41000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>40200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>42800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>43900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>44000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>142800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>142600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>146500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>146800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>148800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>152600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>155000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>151400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>146300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5800,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5600000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5763800</v>
+      </c>
+      <c r="F54" s="3">
         <v>5777900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5763000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5531200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5642200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5686600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5808700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5847700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5760000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5947800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6199500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6565000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6280900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6318000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>6397300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6369700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6290600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6251100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6276600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6165800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>5390500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>5244200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>5289700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5113700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>5157700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>4426100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>4361700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>4244900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>4215900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>4065000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>4075400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>4156800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>4008600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>4110700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>4008900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>3982500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>3924100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>2482000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5970,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,204 +6014,212 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>143100</v>
+      </c>
+      <c r="F57" s="3">
         <v>140000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>128600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>138200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>141900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>141200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>103500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>130800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>161600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>148500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>114200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>179200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>162400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>151300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>104100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>137900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>116500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>98300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>64400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>86300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>74600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>59700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>62100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>126800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>141700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>96400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>80200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>106200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>118600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>80800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>58200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>94700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>103500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>71600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>51300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>88800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>90800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>634400</v>
+        <v>109600</v>
       </c>
       <c r="E58" s="3">
         <v>625500</v>
       </c>
       <c r="F58" s="3">
+        <v>634400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>625500</v>
+      </c>
+      <c r="H58" s="3">
         <v>618300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>91600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>91900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>107700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>107900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>108000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>106100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>106000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>106200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>67800</v>
-      </c>
-      <c r="P58" s="3">
-        <v>63700</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>63700</v>
       </c>
       <c r="R58" s="3">
         <v>63700</v>
       </c>
       <c r="S58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="T58" s="3">
+        <v>63700</v>
+      </c>
+      <c r="U58" s="3">
         <v>114800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>114100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>113500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>112800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>63700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>63700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>63600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>63600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>63800</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>48500</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>48500</v>
       </c>
       <c r="AD58" s="3">
         <v>48500</v>
@@ -5960,13 +6228,13 @@
         <v>48500</v>
       </c>
       <c r="AF58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>48500</v>
+      </c>
+      <c r="AH58" s="3">
         <v>38500</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>38400</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>38400</v>
       </c>
       <c r="AI58" s="3">
         <v>38400</v>
@@ -5984,474 +6252,504 @@
         <v>38400</v>
       </c>
       <c r="AN58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>38400</v>
+      </c>
+      <c r="AP58" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>851600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1085500</v>
+      </c>
+      <c r="F59" s="3">
         <v>655900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>742100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>890600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1039200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>666700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>712100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>860700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1002200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>693900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>660600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>882100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1112500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>895800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>662000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>953400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1036500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>766000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>539200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>783400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>811900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>480100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>429700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>728000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>766000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>574200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>486100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>607100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>623300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>474400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>401100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>526400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>567600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>494600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>400700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>503600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>525900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>420500</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1323400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1937000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1667600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1632600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1786700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1363700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1106500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1040700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1228800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1362800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1130700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>986400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1287900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1342700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1110900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>829900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1155000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1267800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>978400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>717100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>982500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>950200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>603500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>555400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>918400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>971500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>719100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>614900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>761800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>790400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>593600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>497800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>659500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>709600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>604600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>490400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>630800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>655000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>506500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3069700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2794500</v>
+      </c>
+      <c r="F61" s="3">
         <v>2809900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2326700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2348500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2943300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2966600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2855100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2890300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2897500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2919000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2948100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2974100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2769700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2670300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2687500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2695600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2704600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2736200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2740000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2768000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2387900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2387100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2365400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1817100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2005100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>1527700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1310900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>1345300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>1487000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>1234300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1078000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>1182300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>1262300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>1234000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>1168200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>1216700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>1371800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>686900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>297900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>300000</v>
+      </c>
+      <c r="F62" s="3">
         <v>294500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>288500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>301600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>310300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>311800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>306200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>291300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>285500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>286300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>264200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>237500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>616700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>689400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>814800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>725400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>651700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>707400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>792900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>728900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>676700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>722000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>738600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>728000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>658800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>452400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>542700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>454800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>388700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>425400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>495500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>434200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>427300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>473200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>562000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>454400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>370500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>400200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6864,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6986,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7108,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4955200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5295700</v>
+      </c>
+      <c r="F66" s="3">
         <v>5024000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4527100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4715100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4896900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4661700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4486700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4697000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4831800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4612100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4600000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4787600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5016000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4705600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4568000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4804200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4858100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4656500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4494400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4705100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4224400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>3927500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3867500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>3688200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3855300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>2925500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>2695400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>2781600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>2876300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2475600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>2304800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2511500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2607200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2539600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>2432100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>2504600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>2585800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>1607500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7278,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7396,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7518,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7640,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7762,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>583000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>452100</v>
+      </c>
+      <c r="F72" s="3">
         <v>718700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>997400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>687200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>524500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>766800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1039000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>760800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>619700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>873700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1081000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>837600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>705900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>895900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1081500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>786500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>598800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>773800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>914600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>639900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>492100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>645900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>799500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>717600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>582200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>759800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>920300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>699000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>551900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>726700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>869900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>673100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>480000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>551000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>650300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>511500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>394700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>486700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8006,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8128,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8250,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>301800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>156500</v>
+      </c>
+      <c r="F76" s="3">
         <v>424500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>895400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>530700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>444100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>709900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1003500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>829900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>633000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1003900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1273900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1462600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1264900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1612400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1829300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1565500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1432500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1594600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1782200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1460700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1166100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1316700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1422100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1425500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1302500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1500600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1666400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1463300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1339600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1589400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>1770700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>1645300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>1401400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>1571200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>1576700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>1477900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>1338300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>874500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8494,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-186800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-185500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>392800</v>
       </c>
-      <c r="F81" s="3">
-        <v>245500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-172800</v>
-      </c>
       <c r="H81" s="3">
+        <v>244400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-173300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-174700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>362000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>219300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-175500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-128600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>325000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>208700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-137000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-108700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>372600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>223400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-139300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-140800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>274600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>147800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-153800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-153600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>152500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>206400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>292100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>206300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-107800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-83700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>256300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>235700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-28400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-57100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>181100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>149200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-62600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8791,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>71500</v>
+      </c>
+      <c r="F83" s="3">
         <v>69800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>68500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>69400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>66700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>63700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>69100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>66000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>64600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>58000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>65700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>62100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>64600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>63200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>65700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>62100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>61500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>63200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>64100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>62700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>62600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>63200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>64700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>63800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>57800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>56600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>55300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>55200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>50300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>54100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>51400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>48600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>48900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>50000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>49600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>40600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9031,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9153,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9275,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9397,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9519,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>259900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>315900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-171600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>117700</v>
       </c>
-      <c r="F89" s="3">
-        <v>326300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>282400</v>
-      </c>
       <c r="H89" s="3">
+        <v>326400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>282700</v>
+      </c>
+      <c r="J89" s="3">
         <v>-92000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>109900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>242700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>328500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-87300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>121400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>272500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>333000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-62500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>161700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>262300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>349000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-25900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>92100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>347100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>112000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-72000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-70700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>328400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>209300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>159400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>329100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>177100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-31700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>149600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>265500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>155400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-37300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>164300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>272900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>57000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9689,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-71700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-55900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-33200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-75000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-71000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-56100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-24800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-76900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-53400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-53700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-54700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-82500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-124100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-33000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-78700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-50100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-29500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-18300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-37200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-30200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-69200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-52600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-45100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-65700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-47900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-34300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-49900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-94800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-92100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9929,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10051,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-74300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-71700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-49000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-27500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-57000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-71000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-150200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-71600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>5600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-51900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-71500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-134500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-92400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-30000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-185700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-39900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-28300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-9300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-36500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-29300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-26300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-20700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-69000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-376800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-43400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-148300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-63700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-340700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-18100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-41700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-550200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,65 +10221,67 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>79800</v>
+      </c>
+      <c r="F96" s="3">
         <v>79700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>82500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>82800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>83100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>83200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>83800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>78200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>78500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>78700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>81600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>77000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-77000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-76900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-77500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-35700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-35600</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9824,55 +10292,61 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-70700</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-71000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-71100</v>
       </c>
       <c r="AB96" s="3">
         <v>-71000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-70900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-59200</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-59500</v>
       </c>
       <c r="AG96" s="3">
         <v>-59500</v>
       </c>
       <c r="AH96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-42600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-42200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-42300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-29400</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-29300</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10461,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10583,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10705,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-392200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="F100" s="3">
         <v>194900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-134800</v>
       </c>
-      <c r="F100" s="3">
-        <v>-170400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-132300</v>
-      </c>
       <c r="H100" s="3">
+        <v>-170600</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-132600</v>
+      </c>
+      <c r="J100" s="3">
         <v>-143600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-182300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-97600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-153600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-212500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-501800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-96700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-104600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-140500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-132000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-136000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-84700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-39700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-39000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>526000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-12700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>4900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>441200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-268300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>198400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>125100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-119600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>135900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>63200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-191800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-133500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-88600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>11300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-87600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-195200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>543400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>43900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-11400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>11700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-13200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>6200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-18900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-18900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>2400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>2900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>1800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-6100</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>4600</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-3500</v>
       </c>
       <c r="AJ101" s="3">
         <v>4600</v>
       </c>
       <c r="AK101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="AL101" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AM101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-194700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>144200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-24400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-23700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>86100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>81400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-379800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-108600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>85100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>167300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-345500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>118300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>75000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-60200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>224300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-97800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>44400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>839600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>70300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>352700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>32000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>49900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-110800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>26300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-67200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>88700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>29300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-78400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>54900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>34200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>38900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-700</v>
       </c>
     </row>
